--- a/reports_sample/แบบฟอร์มบัญชีคุมวัสดุสิ้นเปลือง_ตัวอย่าง.xlsx
+++ b/reports_sample/แบบฟอร์มบัญชีคุมวัสดุสิ้นเปลือง_ตัวอย่าง.xlsx
@@ -421,7 +421,7 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>ส่วนราชการ: คณะพยาบาลศาสตร์       หน่วยงานผู้ครอบครอง: ศูนย์ฝึกทักษะการพยาบาล (Nursing Lab)       ประเภท: วัสดุการแพทย์และเวชภัณฑ์สิ้นเปลือง</v>
+        <v>ส่วนราชการ: คณะพยาบาลศาสตร์ มหาวิทยาลัยเกษตรศาสตร์       หน่วยงานผู้ครอบครอง: ศูนย์การเรียนรู้ปฏิบัติการทางการพยาบาลเสมือนจริง       ประเภท: วัสดุการแพทย์และเวชภัณฑ์สิ้นเปลือง</v>
       </c>
     </row>
     <row r="3">
@@ -610,7 +610,7 @@
         <v>เซต</v>
       </c>
       <c r="F9" t="str">
-        <v>ศูนย์ฝึกทักษะการพยาบาล</v>
+        <v>ศูนย์การเรียนรู้ปฏิบัติการทางการพยาบาลเสมือนจริง</v>
       </c>
       <c r="G9" t="str">
         <v>9999</v>
@@ -692,7 +692,7 @@
         <v>กล่อง</v>
       </c>
       <c r="F11" t="str">
-        <v>ศูนย์ฝึกทักษะการพยาบาล</v>
+        <v>ศูนย์การเรียนรู้ปฏิบัติการทางการพยาบาลเสมือนจริง</v>
       </c>
       <c r="G11" t="str">
         <v>9999</v>
@@ -733,7 +733,7 @@
         <v>กล่อง</v>
       </c>
       <c r="F12" t="str">
-        <v>ศูนย์ฝึกทักษะการพยาบาล</v>
+        <v>ศูนย์การเรียนรู้ปฏิบัติการทางการพยาบาลเสมือนจริง</v>
       </c>
       <c r="G12" t="str">
         <v>9999</v>
@@ -774,7 +774,7 @@
         <v>ขวด</v>
       </c>
       <c r="F13" t="str">
-        <v>ศูนย์ฝึกทักษะการพยาบาล</v>
+        <v>ศูนย์การเรียนรู้ปฏิบัติการทางการพยาบาลเสมือนจริง</v>
       </c>
       <c r="G13" t="str">
         <v>อว 6501.38/1429</v>
@@ -815,7 +815,7 @@
         <v>ขวด</v>
       </c>
       <c r="F14" t="str">
-        <v>ศูนย์ฝึกทักษะการพยาบาล</v>
+        <v>ศูนย์การเรียนรู้ปฏิบัติการทางการพยาบาลเสมือนจริง</v>
       </c>
       <c r="G14" t="str">
         <v>อว 6501.38/1106</v>
@@ -856,7 +856,7 @@
         <v>ขวด</v>
       </c>
       <c r="F15" t="str">
-        <v>ศูนย์ฝึกทักษะการพยาบาล</v>
+        <v>ศูนย์การเรียนรู้ปฏิบัติการทางการพยาบาลเสมือนจริง</v>
       </c>
       <c r="G15" t="str">
         <v>อว 6501.38/1429</v>
@@ -897,7 +897,7 @@
         <v>ขวด</v>
       </c>
       <c r="F16" t="str">
-        <v>ศูนย์ฝึกทักษะการพยาบาล</v>
+        <v>ศูนย์การเรียนรู้ปฏิบัติการทางการพยาบาลเสมือนจริง</v>
       </c>
       <c r="G16" t="str">
         <v>อว 6501.38/1106</v>
@@ -938,7 +938,7 @@
         <v>กล่อง</v>
       </c>
       <c r="F17" t="str">
-        <v>ศูนย์ฝึกทักษะการพยาบาล</v>
+        <v>ศูนย์การเรียนรู้ปฏิบัติการทางการพยาบาลเสมือนจริง</v>
       </c>
       <c r="G17" t="str">
         <v>9999</v>
@@ -979,7 +979,7 @@
         <v>กล่อง</v>
       </c>
       <c r="F18" t="str">
-        <v>ศูนย์ฝึกทักษะการพยาบาล</v>
+        <v>ศูนย์การเรียนรู้ปฏิบัติการทางการพยาบาลเสมือนจริง</v>
       </c>
       <c r="G18" t="str">
         <v>9999</v>
@@ -1020,7 +1020,7 @@
         <v>ขวด</v>
       </c>
       <c r="F19" t="str">
-        <v>ศูนย์ฝึกทักษะการพยาบาล</v>
+        <v>ศูนย์การเรียนรู้ปฏิบัติการทางการพยาบาลเสมือนจริง</v>
       </c>
       <c r="G19" t="str">
         <v>9999</v>
@@ -1061,7 +1061,7 @@
         <v>แพ๊ค</v>
       </c>
       <c r="F20" t="str">
-        <v>ศูนย์ฝึกทักษะการพยาบาล</v>
+        <v>ศูนย์การเรียนรู้ปฏิบัติการทางการพยาบาลเสมือนจริง</v>
       </c>
       <c r="G20" t="str">
         <v>111</v>
@@ -1102,7 +1102,7 @@
         <v>แพ๊ค</v>
       </c>
       <c r="F21" t="str">
-        <v>ศูนย์ฝึกทักษะการพยาบาล</v>
+        <v>ศูนย์การเรียนรู้ปฏิบัติการทางการพยาบาลเสมือนจริง</v>
       </c>
       <c r="G21" t="str">
         <v>1414</v>
@@ -1143,7 +1143,7 @@
         <v>กล่อง</v>
       </c>
       <c r="F22" t="str">
-        <v>ศูนย์ฝึกทักษะการพยาบาล</v>
+        <v>ศูนย์การเรียนรู้ปฏิบัติการทางการพยาบาลเสมือนจริง</v>
       </c>
       <c r="G22" t="str">
         <v>อว 6501.38/1429</v>
@@ -1184,7 +1184,7 @@
         <v>กล่อง</v>
       </c>
       <c r="F23" t="str">
-        <v>ศูนย์ฝึกทักษะการพยาบาล</v>
+        <v>ศูนย์การเรียนรู้ปฏิบัติการทางการพยาบาลเสมือนจริง</v>
       </c>
       <c r="G23" t="str">
         <v>อว 6501.38/1429</v>
@@ -1225,7 +1225,7 @@
         <v>กล่อง</v>
       </c>
       <c r="F24" t="str">
-        <v>ศูนย์ฝึกทักษะการพยาบาล</v>
+        <v>ศูนย์การเรียนรู้ปฏิบัติการทางการพยาบาลเสมือนจริง</v>
       </c>
       <c r="G24" t="str">
         <v>9999</v>
@@ -1266,7 +1266,7 @@
         <v>กล่อง</v>
       </c>
       <c r="F25" t="str">
-        <v>ศูนย์ฝึกทักษะการพยาบาล</v>
+        <v>ศูนย์การเรียนรู้ปฏิบัติการทางการพยาบาลเสมือนจริง</v>
       </c>
       <c r="G25" t="str">
         <v>อว 6501.38/1429</v>
@@ -1307,7 +1307,7 @@
         <v>กล่อง</v>
       </c>
       <c r="F26" t="str">
-        <v>ศูนย์ฝึกทักษะการพยาบาล</v>
+        <v>ศูนย์การเรียนรู้ปฏิบัติการทางการพยาบาลเสมือนจริง</v>
       </c>
       <c r="G26" t="str">
         <v>9999</v>
@@ -1348,7 +1348,7 @@
         <v>กล่อง</v>
       </c>
       <c r="F27" t="str">
-        <v>ศูนย์ฝึกทักษะการพยาบาล</v>
+        <v>ศูนย์การเรียนรู้ปฏิบัติการทางการพยาบาลเสมือนจริง</v>
       </c>
       <c r="G27" t="str">
         <v>9999</v>
@@ -1389,7 +1389,7 @@
         <v>กล่อง</v>
       </c>
       <c r="F28" t="str">
-        <v>ศูนย์ฝึกทักษะการพยาบาล</v>
+        <v>ศูนย์การเรียนรู้ปฏิบัติการทางการพยาบาลเสมือนจริง</v>
       </c>
       <c r="G28" t="str">
         <v>อว 6501.38/1429</v>
@@ -1430,7 +1430,7 @@
         <v>กล่อง</v>
       </c>
       <c r="F29" t="str">
-        <v>ศูนย์ฝึกทักษะการพยาบาล</v>
+        <v>ศูนย์การเรียนรู้ปฏิบัติการทางการพยาบาลเสมือนจริง</v>
       </c>
       <c r="G29" t="str">
         <v>9999</v>
@@ -1471,7 +1471,7 @@
         <v>กล่อง</v>
       </c>
       <c r="F30" t="str">
-        <v>ศูนย์ฝึกทักษะการพยาบาล</v>
+        <v>ศูนย์การเรียนรู้ปฏิบัติการทางการพยาบาลเสมือนจริง</v>
       </c>
       <c r="G30" t="str">
         <v>อว 6501.38/1429</v>
@@ -1512,7 +1512,7 @@
         <v>กล่อง</v>
       </c>
       <c r="F31" t="str">
-        <v>ศูนย์ฝึกทักษะการพยาบาล</v>
+        <v>ศูนย์การเรียนรู้ปฏิบัติการทางการพยาบาลเสมือนจริง</v>
       </c>
       <c r="G31" t="str">
         <v>อว 6501.38/1429</v>
